--- a/documentos/Dashboard de ventas.xlsx
+++ b/documentos/Dashboard de ventas.xlsx
@@ -122,7 +122,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -158,11 +158,104 @@
         <color rgb="00E39B2B"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00E39B2B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00E39B2B"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00E39B2B"/>
+      </right>
+      <top style="medium">
+        <color rgb="00E39B2B"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00E39B2B"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00E39B2B"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00E39B2B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00E39B2B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00E39B2B"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00E39B2B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00E39B2B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00E39B2B"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00E39B2B"/>
+      </right>
+      <top style="medium">
+        <color rgb="00E39B2B"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00E39B2B"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -240,6 +333,13 @@
     <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -318,7 +418,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -359,7 +458,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1B3A4B"/>
+                <a:srgbClr val="1F4E4A"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -440,7 +539,6 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -478,7 +576,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1B3A4B"/>
+                <a:srgbClr val="1F4E4A"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -489,7 +587,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E39B2B"/>
+                <a:srgbClr val="E0A020"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -533,7 +631,7 @@
             <idx val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2E75B6"/>
+                <a:srgbClr val="2E5090"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -975,17 +1073,6 @@
           <t>DASHBOARD DE VENTAS</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="2" t="n"/>
-      <c r="L1" s="2" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -993,17 +1080,6 @@
           <t>Resumen visual para el gerente — septiembre 2026</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
     </row>
     <row r="3" ht="10" customHeight="1"/>
     <row r="4" ht="22" customHeight="1">
@@ -1012,66 +1088,66 @@
           <t>Ventas totales</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
+      <c r="B4" s="29" t="n"/>
+      <c r="C4" s="30" t="n"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Cumplen meta</t>
         </is>
       </c>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="F4" s="29" t="n"/>
+      <c r="G4" s="30" t="n"/>
       <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Ventas destacadas</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
+      <c r="I4" s="29" t="n"/>
+      <c r="J4" s="30" t="n"/>
       <c r="K4" s="5" t="inlineStr">
         <is>
           <t>A revisar</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n"/>
+      <c r="L4" s="30" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="7">
         <f>KPIs!B2</f>
         <v/>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
+      <c r="B5" s="31" t="n"/>
+      <c r="C5" s="32" t="n"/>
       <c r="E5" s="9">
         <f>KPIs!B3</f>
         <v/>
       </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="32" t="n"/>
       <c r="H5" s="9">
         <f>KPIs!B4</f>
         <v/>
       </c>
-      <c r="I5" s="8" t="n"/>
-      <c r="J5" s="8" t="n"/>
+      <c r="I5" s="31" t="n"/>
+      <c r="J5" s="32" t="n"/>
       <c r="K5" s="9">
         <f>KPIs!B5</f>
         <v/>
       </c>
-      <c r="L5" s="8" t="n"/>
+      <c r="L5" s="32" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
+      <c r="A6" s="33" t="n"/>
+      <c r="B6" s="34" t="n"/>
+      <c r="C6" s="35" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="35" t="n"/>
+      <c r="H6" s="33" t="n"/>
+      <c r="I6" s="34" t="n"/>
+      <c r="J6" s="35" t="n"/>
+      <c r="K6" s="33" t="n"/>
+      <c r="L6" s="35" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
@@ -1277,7 +1353,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>70500</v>
+        <v>73000</v>
       </c>
     </row>
     <row r="3">
@@ -1297,7 +1373,7 @@
         </is>
       </c>
       <c r="B4" s="23" t="n">
-        <v>87000</v>
+        <v>67000</v>
       </c>
     </row>
     <row r="5">
@@ -1317,7 +1393,7 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>74800</v>
+        <v>78800</v>
       </c>
     </row>
     <row r="7">
@@ -1347,7 +1423,7 @@
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>45200</v>
+        <v>44200</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1369,7 +1445,7 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>305900</v>
+        <v>305500</v>
       </c>
     </row>
     <row r="14">
@@ -1379,7 +1455,7 @@
         </is>
       </c>
       <c r="B14" s="25" t="n">
-        <v>178200</v>
+        <v>178300</v>
       </c>
     </row>
     <row r="15">
@@ -1389,7 +1465,7 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>87800</v>
+        <v>87200</v>
       </c>
     </row>
     <row r="16">

--- a/documentos/Dashboard de ventas.xlsx
+++ b/documentos/Dashboard de ventas.xlsx
@@ -11,7 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KPIs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Dashboard'!$1:$2</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,48 +35,57 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="001F2933"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
+      <color rgb="001F2933"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001B3A4B"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="24"/>
     </font>
     <font>
       <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="001B3A4B"/>
-      <sz val="11"/>
+      <color rgb="00D6E2EA"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="20"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="001B3A4B"/>
+      <sz val="22"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -83,12 +94,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="001B3A4B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6E3F0"/>
+        <fgColor rgb="00E7F0F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -98,31 +114,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FFF3D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001B3A4B"/>
+        <fgColor rgb="00F4F7FA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF2"/>
+        <fgColor rgb="00243E52"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E39B2B"/>
+        <fgColor rgb="00E08A1E"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8F0"/>
+        <fgColor rgb="00FFF8EF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -130,216 +146,115 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
     <border>
       <left style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </left>
       <right style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </right>
       <top style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B0B8C4"/>
+        <color rgb="00D5DEE7"/>
       </bottom>
     </border>
     <border>
       <left style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </left>
       <right style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </right>
       <top style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </top>
-      <bottom style="medium">
-        <color rgb="00E39B2B"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00E39B2B"/>
-      </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </left>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color rgb="00E08A1E"/>
+      </right>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00E39B2B"/>
-      </right>
-      <top style="medium">
-        <color rgb="00E39B2B"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00E39B2B"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <left style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </left>
-      <right/>
-      <top/>
+      <right style="medium">
+        <color rgb="00E08A1E"/>
+      </right>
       <bottom style="medium">
-        <color rgb="00E39B2B"/>
+        <color rgb="00E08A1E"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="00E39B2B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00E39B2B"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="00E39B2B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="00E39B2B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00E39B2B"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="00E39B2B"/>
-      </right>
-      <top style="medium">
-        <color rgb="00E39B2B"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="00E39B2B"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="10" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,6 +333,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -443,7 +359,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Datos'!B12</f>
+              <f>'Datos'!B16</f>
             </strRef>
           </tx>
           <spPr>
@@ -458,7 +374,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1F4E4A"/>
+                <a:srgbClr val="1B3A4B"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -469,7 +385,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E39B2B"/>
+                <a:srgbClr val="E08A1E"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -487,21 +403,25 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dLbls>
+            <numFmt formatCode="&quot;$&quot;#,##0"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+          </dLbls>
           <cat>
             <numRef>
-              <f>'Datos'!$A$13:$A$15</f>
+              <f>'Datos'!$A$17:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Datos'!$B$13:$B$15</f>
+              <f>'Datos'!$B$17:$B$19</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
+        <gapWidth val="50"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -524,7 +444,13 @@
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -539,6 +465,7 @@
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -564,10 +491,13 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Datos'!B1</f>
+              <f>'Datos'!B3</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B3A4B"/>
+            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
@@ -576,7 +506,7 @@
             <idx val="0"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1F4E4A"/>
+                <a:srgbClr val="1B3A4B"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -587,7 +517,7 @@
             <idx val="1"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="E0A020"/>
+                <a:srgbClr val="E08A1E"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -609,7 +539,7 @@
             <idx val="3"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2E8B57"/>
+                <a:srgbClr val="1E7A46"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -631,7 +561,7 @@
             <idx val="5"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="2E5090"/>
+                <a:srgbClr val="2E75B6"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -642,7 +572,7 @@
             <idx val="6"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7DCEA0"/>
+                <a:srgbClr val="148F77"/>
               </a:solidFill>
               <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
@@ -660,21 +590,25 @@
               </a:ln>
             </spPr>
           </dPt>
+          <dLbls>
+            <numFmt formatCode="&quot;$&quot;#,##0"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+          </dLbls>
           <cat>
             <numRef>
-              <f>'Datos'!$A$2:$A$9</f>
+              <f>'Datos'!$A$4:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Datos'!$B$2:$B$9</f>
+              <f>'Datos'!$B$4:$B$11</f>
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showVal val="1"/>
-        </dLbls>
-        <gapWidth val="150"/>
+        <gapWidth val="50"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -693,11 +627,17 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="130000"/>
+          <max val="140000"/>
           <min val="0"/>
         </scaling>
         <axPos val="l"/>
-        <majorGridlines/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -714,12 +654,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>3</col>
+      <col>4</col>
       <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2880000"/>
+    <ext cx="5040000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -736,12 +676,12 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>8</col>
+      <col>4</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>23</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5760000" cy="2880000"/>
+    <ext cx="6480000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -1045,278 +985,916 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00E08A1E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="3" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>DASHBOARD DE VENTAS</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Resumen visual para el gerente — septiembre 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="10" customHeight="1"/>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+          <t>Resumen visual para el gerente  ·  septiembre 2026</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="n"/>
+      <c r="N2" s="4" t="n"/>
+      <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
+    </row>
+    <row r="3" ht="14" customHeight="1">
+      <c r="A3" s="5" t="n"/>
+      <c r="B3" s="5" t="n"/>
+      <c r="C3" s="5" t="n"/>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+      <c r="H3" s="5" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="5" t="n"/>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Ventas totales</t>
         </is>
       </c>
-      <c r="B4" s="29" t="n"/>
-      <c r="C4" s="30" t="n"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="B4" s="7" t="n"/>
+      <c r="C4" s="7" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Cumplen meta</t>
         </is>
       </c>
-      <c r="F4" s="29" t="n"/>
-      <c r="G4" s="30" t="n"/>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="F4" s="7" t="n"/>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="5" t="n"/>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Ventas destacadas</t>
         </is>
       </c>
-      <c r="I4" s="29" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>A revisar</t>
         </is>
       </c>
-      <c r="L4" s="30" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="7">
-        <f>KPIs!B2</f>
-        <v/>
-      </c>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="32" t="n"/>
-      <c r="E5" s="9">
-        <f>KPIs!B3</f>
-        <v/>
-      </c>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="32" t="n"/>
-      <c r="H5" s="9">
-        <f>KPIs!B4</f>
-        <v/>
-      </c>
-      <c r="I5" s="31" t="n"/>
-      <c r="J5" s="32" t="n"/>
-      <c r="K5" s="9">
-        <f>KPIs!B5</f>
-        <v/>
-      </c>
-      <c r="L5" s="32" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="33" t="n"/>
-      <c r="B6" s="34" t="n"/>
-      <c r="C6" s="35" t="n"/>
-      <c r="E6" s="33" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="35" t="n"/>
-      <c r="H6" s="33" t="n"/>
-      <c r="I6" s="34" t="n"/>
-      <c r="J6" s="35" t="n"/>
-      <c r="K6" s="33" t="n"/>
-      <c r="L6" s="35" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="N4" s="7" t="n"/>
+      <c r="O4" s="7" t="n"/>
+      <c r="P4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="8" t="n">
+        <v>581900</v>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="N5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
+      <c r="P5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="5" t="n"/>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>Región</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11">
-        <f>Datos!A2</f>
-        <v/>
-      </c>
-      <c r="B9" s="12">
-        <f>Datos!B2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13">
-        <f>Datos!A3</f>
-        <v/>
-      </c>
-      <c r="B10" s="14">
-        <f>Datos!B3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11">
-        <f>Datos!A4</f>
-        <v/>
-      </c>
-      <c r="B11" s="12">
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Norte</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
         <f>Datos!B4</f>
         <v/>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13">
-        <f>Datos!A5</f>
-        <v/>
-      </c>
-      <c r="B12" s="14">
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="B10" s="16">
         <f>Datos!B5</f>
         <v/>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11">
-        <f>Datos!A6</f>
-        <v/>
-      </c>
-      <c r="B13" s="12">
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Occidente</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
         <f>Datos!B6</f>
         <v/>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13">
-        <f>Datos!A7</f>
-        <v/>
-      </c>
-      <c r="B14" s="14">
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Sur</t>
+        </is>
+      </c>
+      <c r="B12" s="16">
         <f>Datos!B7</f>
         <v/>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11">
-        <f>Datos!A8</f>
-        <v/>
-      </c>
-      <c r="B15" s="12">
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Sureste</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
         <f>Datos!B8</f>
         <v/>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13">
-        <f>Datos!A9</f>
-        <v/>
-      </c>
-      <c r="B16" s="14">
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+      <c r="H13" s="5" t="n"/>
+      <c r="I13" s="5" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Noroeste</t>
+        </is>
+      </c>
+      <c r="B14" s="16">
         <f>Datos!B9</f>
         <v/>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+      <c r="H14" s="5" t="n"/>
+      <c r="I14" s="5" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Bajío</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <f>Datos!B10</f>
+        <v/>
+      </c>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+      <c r="H15" s="5" t="n"/>
+      <c r="I15" s="5" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
+      <c r="M15" s="5" t="n"/>
+      <c r="N15" s="5" t="n"/>
+      <c r="O15" s="5" t="n"/>
+      <c r="P15" s="5" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Golfo</t>
+        </is>
+      </c>
+      <c r="B16" s="16">
+        <f>Datos!B11</f>
+        <v/>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="5" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
+      <c r="M17" s="5" t="n"/>
+      <c r="N17" s="5" t="n"/>
+      <c r="O17" s="5" t="n"/>
+      <c r="P17" s="5" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15">
-        <f>Datos!A13</f>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="5" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Smartphone</t>
+        </is>
+      </c>
+      <c r="B19" s="14">
+        <f>Datos!B17</f>
         <v/>
       </c>
-      <c r="B19" s="16">
-        <f>Datos!B13</f>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="5" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>Impresora</t>
+        </is>
+      </c>
+      <c r="B20" s="16">
+        <f>Datos!B18</f>
         <v/>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17">
-        <f>Datos!A14</f>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Bocina</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>Datos!B19</f>
         <v/>
       </c>
-      <c r="B20" s="18">
-        <f>Datos!B14</f>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="18">
+        <f>Datos!B20</f>
         <v/>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15">
-        <f>Datos!A15</f>
-        <v/>
-      </c>
-      <c r="B21" s="16">
-        <f>Datos!B15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>Datos!B16</f>
-        <v/>
-      </c>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="5" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
+      <c r="M22" s="5" t="n"/>
+      <c r="N22" s="5" t="n"/>
+      <c r="O22" s="5" t="n"/>
+      <c r="P22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n"/>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="5" t="n"/>
+      <c r="L32" s="5" t="n"/>
+      <c r="M32" s="5" t="n"/>
+      <c r="N32" s="5" t="n"/>
+      <c r="O32" s="5" t="n"/>
+      <c r="P32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n"/>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n"/>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n"/>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n"/>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n"/>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n"/>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n"/>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n"/>
+      <c r="B40" s="5" t="n"/>
+      <c r="C40" s="5" t="n"/>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n"/>
+      <c r="B41" s="5" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:P1"/>
     <mergeCell ref="A5:C6"/>
-    <mergeCell ref="A1:L1"/>
     <mergeCell ref="E5:G6"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="H5:J6"/>
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="I5:K6"/>
+    <mergeCell ref="M5:O6"/>
     <mergeCell ref="E4:G4"/>
-    <mergeCell ref="K5:L6"/>
-    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="I4:K4"/>
     <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:P2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.35" right="0.35" top="0.4" bottom="0.4" header="0.15" footer="0.15"/>
   <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CDashboard de ventas</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -1324,250 +1902,270 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Ventas por región</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n"/>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Región</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Norte</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n">
+      <c r="B4" s="14" t="n">
         <v>73000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Centro</t>
         </is>
       </c>
-      <c r="B3" s="25" t="n">
+      <c r="B5" s="16" t="n">
         <v>78000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Occidente</t>
         </is>
       </c>
-      <c r="B4" s="23" t="n">
+      <c r="B6" s="14" t="n">
         <v>67000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Sur</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B7" s="16" t="n">
         <v>111200</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="22" t="inlineStr">
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Sureste</t>
         </is>
       </c>
-      <c r="B6" s="23" t="n">
+      <c r="B8" s="14" t="n">
         <v>78800</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Noroeste</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B9" s="16" t="n">
         <v>66800</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>Bajío</t>
         </is>
       </c>
-      <c r="B8" s="23" t="n">
+      <c r="B10" s="14" t="n">
         <v>42800</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Golfo</t>
         </is>
       </c>
-      <c r="B9" s="25" t="n">
+      <c r="B11" s="16" t="n">
         <v>44200</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="21" t="inlineStr">
+    <row r="14" ht="38" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Ventas por producto</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="22" t="inlineStr">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Smartphone</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n">
+      <c r="B17" s="14" t="n">
         <v>305500</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Impresora</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B18" s="16" t="n">
         <v>178300</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="22" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Bocina</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B19" s="14" t="n">
         <v>87200</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B16" s="20">
-        <f>SUM(B13:B15)</f>
+      <c r="B20" s="18">
+        <f>SUM(B17:B19)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CDatos</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <mergeCells count="2">
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="21" t="inlineStr">
+    <row r="1" ht="38" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Indicadores</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n"/>
+    </row>
+    <row r="2" ht="8" customHeight="1"/>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="B1" s="21" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Ventas totales</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n">
+      <c r="B4" s="14" t="n">
         <v>581900</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="24" t="inlineStr">
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Cumplen meta</t>
         </is>
       </c>
-      <c r="B3" s="27" t="n">
+      <c r="B5" s="22" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Ventas destacadas</t>
         </is>
       </c>
-      <c r="B4" s="28" t="n">
+      <c r="B6" s="23" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>A revisar</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B7" s="22" t="n">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="3" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CKPIs</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="3" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>